--- a/main/CodeSystem-bc-operation-outcome-details-code-system.xlsx
+++ b/main/CodeSystem-bc-operation-outcome-details-code-system.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-27T22:33:33+00:00</t>
+    <t>2026-03-25T22:00:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
